--- a/601166_CIB/601166_CIB.xlsx
+++ b/601166_CIB/601166_CIB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18803\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\PythonProject\A-share-Bank-Financial-Report-Analysis\601166_CIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31A5C10-499B-46C3-80B2-BF69EAF2725B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72962D69-2D1C-428A-9C89-F46AA89DEC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6540" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="35">
   <si>
     <t>营业收入</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,10 +48,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每股现金流净额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>平均资产收益率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -160,18 +156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>人民币流动性比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外币流动性比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流动性覆盖率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>正常类贷款迁徙率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -185,10 +169,6 @@
   </si>
   <si>
     <t>可疑类贷款迁徙率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经现流</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -537,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -563,305 +543,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>653656</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>3.21</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>3.44</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>30.89</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.72</v>
+        <v>11094256</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>9.1</v>
+        <v>5948938</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>11094256</v>
+        <v>64251</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>5948938</v>
+        <v>146754</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>64251</v>
+        <v>10180610</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>146754</v>
+        <v>1537277</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>10180610</v>
+        <v>2037064</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1537277</v>
+        <v>491495</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>2037064</v>
+        <v>1304833</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>491495</v>
+        <v>821716</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>1304833</v>
+        <v>38.83</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>821716</v>
+        <v>1055170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>38.83</v>
+        <v>764329</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1055170</v>
+        <v>8053631</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>764329</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>8053631</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.5</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>1.71</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>69.92</v>
+        <v>29.56</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>30.08</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>29.56</v>
+        <v>228.41</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>228.41</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.92</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>9.1</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.1</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>13.1</v>
+        <v>36.479999999999997</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>62.38</v>
+        <v>79.33</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>114.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>174.79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>36.479999999999997</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>79.33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>82.52</v>
       </c>
     </row>
@@ -873,7 +813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95170128-8B75-4B3C-B904-1E83CD2631DB}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -898,305 +838,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>-237258</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>3.23</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>3.49</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>-11.42</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.75</v>
+        <v>10507898</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>9.83</v>
+        <v>5736610</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>10507898</v>
+        <v>61477</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>5736610</v>
+        <v>146183</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>61477</v>
+        <v>9614287</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>146183</v>
+        <v>1623797</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>9614287</v>
+        <v>1869121</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1623797</v>
+        <v>444453</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1869121</v>
+        <v>1119989</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>444453</v>
+        <v>766106</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>1119989</v>
+        <v>36.880000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>766106</v>
+        <v>1043880</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>36.880000000000003</v>
+        <v>714164</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1043880</v>
+        <v>7494426</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>714164</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>7494426</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.56</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>1.82</v>
+        <v>30.22</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>69.78</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>30.22</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>29.5</v>
+        <v>237.78</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>237.78</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.92</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>9.25</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.79</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>13.93</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>64.75</v>
+        <v>75.849999999999994</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>81.489999999999995</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>169.24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>30.46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>75.849999999999994</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>76.52</v>
       </c>
     </row>
@@ -1208,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85425F0F-59CE-4DB1-AEFB-6317792C8147}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -1233,305 +1133,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>433617</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>3.48</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>20.87</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.8</v>
+        <v>10158326</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>10.55</v>
+        <v>5460935</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>10158326</v>
+        <v>58491</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>5460935</v>
+        <v>143426</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>58491</v>
+        <v>9350607</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>143426</v>
+        <v>1470318</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>9350607</v>
+        <v>1829352</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1470318</v>
+        <v>376888</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1829352</v>
+        <v>979169</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>376888</v>
+        <v>796224</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>979169</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>796224</v>
+        <v>960834</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>34.200000000000003</v>
+        <v>667283</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>960834</v>
+        <v>6956839</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>667283</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>6956839</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.66</v>
+        <v>69.489999999999995</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>1.93</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>69.489999999999995</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>30.51</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>29.97</v>
+        <v>245.21</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>245.21</v>
+        <v>9.2899999999999991</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>1.23</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>9.2899999999999991</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.52</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>13.81</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>54.06</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>72.83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>156.47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>40.33</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>76.39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>84.69</v>
       </c>
     </row>
@@ -1543,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C7E03-EEF9-4665-8CD6-6DD93ACE52AD}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -1568,305 +1428,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>-344587</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>3.87</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>4.18</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>-16.59</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.03</v>
+        <v>9266671</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>13.79</v>
+        <v>4982887</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>9266671</v>
+        <v>54488</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>4982887</v>
+        <v>128834</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>54488</v>
+        <v>8509373</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>128834</v>
+        <v>1389479</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>8509373</v>
+        <v>1912484</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1389479</v>
+        <v>389794</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1912484</v>
+        <v>695739</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>389794</v>
+        <v>660385</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>695739</v>
+        <v>31.79</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>660385</v>
+        <v>908004</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>31.79</v>
+        <v>621255</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>908004</v>
+        <v>6427244</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>621255</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>6427244</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.83</v>
+        <v>65.33</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2.1</v>
+        <v>34.67</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>65.33</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>34.67</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>29.37</v>
+        <v>236.44</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.0900000000000001</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>236.44</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.76</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>9.34</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.67</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>14.13</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>64.45</v>
+        <v>73.760000000000005</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>64.45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>110.24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>27.46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>73.760000000000005</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>77.959999999999994</v>
       </c>
     </row>
@@ -1878,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5A80D1-36BE-41ED-8116-E82E59B3F5CA}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -1903,305 +1723,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>-389771</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>-18.760000000000002</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.02</v>
+        <v>8603024</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>13.86</v>
+        <v>4428183</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>8603024</v>
+        <v>48714</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>4428183</v>
+        <v>130909</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>48714</v>
+        <v>7908726</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>130909</v>
+        <v>1434288</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>7908726</v>
+        <v>1754633</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1434288</v>
+        <v>334958</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1754633</v>
+        <v>458205</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>334958</v>
+        <v>598309</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>458205</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>598309</v>
+        <v>820158</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>28.8</v>
+        <v>565344</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>820158</v>
+        <v>5818668</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>565344</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>5818668</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>2.02</v>
+        <v>65.849999999999994</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2.29</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>65.849999999999994</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>34.15</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>25.68</v>
+        <v>268.73</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.1000000000000001</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>268.73</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>1.03</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>9.35</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.83</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>14.1</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>56.26</v>
+        <v>50.97</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>56.26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>138.86000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>25.56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>50.97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>30.12</v>
       </c>
     </row>
@@ -2213,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788DE462-357D-41E8-8E9A-DAF92235A9EE}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -2238,305 +2018,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>-34228</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>3.06</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>-1.65</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>0.9</v>
+        <v>7894000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>12.54</v>
+        <v>3965674</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>7894000</v>
+        <v>49656</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>3965674</v>
+        <v>108661</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>49656</v>
+        <v>7269197</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>108661</v>
+        <v>1290261</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>7269197</v>
+        <v>1711733</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1290261</v>
+        <v>324566</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1711733</v>
+        <v>401882</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>324566</v>
+        <v>529784</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>401882</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>529784</v>
+        <v>762803</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>25.5</v>
+        <v>529366</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>762803</v>
+        <v>5663756</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>529366</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>5663756</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>2.11</v>
+        <v>70.650000000000006</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2.36</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>70.650000000000006</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>29.35</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>24.16</v>
+        <v>218.83</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>218.83</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>1.24</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>9.33</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10.85</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>13.47</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>67.39</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>67.39</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>190.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>2.0699999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>31.23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>62.42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>18.03</v>
       </c>
     </row>
